--- a/simulations/AON_nitrous_oxide_100/economics_AON_100.xlsx
+++ b/simulations/AON_nitrous_oxide_100/economics_AON_100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AON_nitrous_oxide_100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA96E4A-F6AE-4E3A-9CC2-89DB3CFCE81F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4926EF2C-AED6-4173-AE5A-D11DC8EBA5CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2609,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:K17"/>
+  <dimension ref="B2:M17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="11"/>
@@ -2623,10 +2623,10 @@
     <col min="10" max="16384" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>23</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="50" t="s">
         <v>102</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>923.47874215069317</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>99</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>925.28</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>100</v>
       </c>
@@ -2711,17 +2711,21 @@
         <f>30690.5025481741/1000</f>
         <v>30.690502548174099</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="42">
         <v>728.17</v>
       </c>
       <c r="F6" s="42">
         <f>D6*E6</f>
         <v>22347.903240503932</v>
       </c>
+      <c r="G6" s="11">
+        <f>F6/Summary!$C$23</f>
+        <v>0.5959429191976231</v>
+      </c>
       <c r="J6" s="49"/>
       <c r="K6" s="49"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="41" t="s">
         <v>103</v>
       </c>
@@ -2732,15 +2736,19 @@
         <f>30690.5025481741/1000</f>
         <v>30.690502548174099</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="42">
         <v>1366.03</v>
       </c>
       <c r="F7" s="42">
         <f>D7*E7</f>
         <v>41924.147195882266</v>
       </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G7" s="11">
+        <f>F7/Summary!$C$23</f>
+        <v>1.1179750688871131</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="50" t="s">
         <v>104</v>
       </c>
@@ -2754,7 +2762,7 @@
       <c r="J8" s="59"/>
       <c r="K8" s="59"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
@@ -2783,7 +2791,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>25</v>
       </c>
@@ -2811,7 +2819,7 @@
         <v>1024.96</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>106</v>
       </c>
@@ -2834,7 +2842,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="36" t="s">
         <v>107</v>
       </c>
@@ -2848,7 +2856,7 @@
         <v>337.4954966024701</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
@@ -2862,7 +2870,7 @@
       <c r="J13" s="59"/>
       <c r="K13" s="59"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
         <v>85</v>
       </c>
@@ -2880,7 +2888,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
         <v>84</v>
       </c>
@@ -2898,8 +2906,14 @@
       <c r="K15" s="42">
         <v>658.84</v>
       </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="11">
+        <v>784.95693082808918</v>
+      </c>
+      <c r="M15" s="11">
+        <v>658.84</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>35</v>
       </c>
@@ -2914,6 +2928,12 @@
         <v>1062.000553473297</v>
       </c>
       <c r="K16" s="42">
+        <v>1191.73</v>
+      </c>
+      <c r="L16" s="11">
+        <v>1062.000553473297</v>
+      </c>
+      <c r="M16" s="11">
         <v>1191.73</v>
       </c>
     </row>

--- a/simulations/AON_nitrous_oxide_100/economics_AON_100.xlsx
+++ b/simulations/AON_nitrous_oxide_100/economics_AON_100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AON_nitrous_oxide_100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4926EF2C-AED6-4173-AE5A-D11DC8EBA5CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D12ECA7-8E5D-4FB0-8618-A1DFF14C83DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{85439D71-B44F-4B1B-84B2-C176EA20096B}">
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{A0720D12-5B32-4944-934D-8F7F547BDFE3}">
       <text>
         <r>
           <rPr>
@@ -1160,7 +1160,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1293,6 +1293,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2668,9 +2671,9 @@
       <c r="J4" s="42">
         <v>728.17</v>
       </c>
-      <c r="K4" s="42">
-        <f>J4*596.2/550.8*596.2/550.8*596.2/550.8</f>
-        <v>923.47874215069317</v>
+      <c r="K4" s="60">
+        <f>J4*596.2/550.8*596.2/550.8*596.2/550.8/(1+0.02)^30</f>
+        <v>509.82573013318409</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
@@ -2901,7 +2904,7 @@
       </c>
       <c r="J15" s="42">
         <f>K4*0.85</f>
-        <v>784.95693082808918</v>
+        <v>433.35187061320647</v>
       </c>
       <c r="K15" s="42">
         <v>658.84</v>
@@ -2925,7 +2928,7 @@
       </c>
       <c r="J16" s="42">
         <f>K4*1.15</f>
-        <v>1062.000553473297</v>
+        <v>586.29958965316166</v>
       </c>
       <c r="K16" s="42">
         <v>1191.73</v>
